--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_araucania.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_araucania.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>26.06843296498469</v>
+      </c>
+      <c r="C2">
         <v>29.20676341365996</v>
-      </c>
-      <c r="C2">
-        <v>26.06843296498469</v>
       </c>
       <c r="D2">
         <v>3.423864485896103</v>
       </c>
       <c r="E2">
-        <v>18.80967733084564</v>
+        <v>16.78853646490699</v>
       </c>
       <c r="F2">
         <v>64.40178620424739</v>
       </c>
       <c r="G2">
-        <v>16.78853646490699</v>
+        <v>18.80967733084564</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>30.73877742736362</v>
+      </c>
+      <c r="C3">
         <v>40.15298933100718</v>
-      </c>
-      <c r="C3">
-        <v>30.73877742736362</v>
       </c>
       <c r="D3">
         <v>2.490474598930481</v>
       </c>
       <c r="E3">
-        <v>23.49615203392492</v>
+        <v>17.98727815297628</v>
       </c>
       <c r="F3">
         <v>58.51656981309879</v>
       </c>
       <c r="G3">
-        <v>17.98727815297628</v>
+        <v>23.49615203392492</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>30.99143429925278</v>
+      </c>
+      <c r="C4">
         <v>45.69892473118279</v>
-      </c>
-      <c r="C4">
-        <v>30.99143429925278</v>
       </c>
       <c r="D4">
         <v>2.188235294117647</v>
       </c>
       <c r="E4">
-        <v>25.86384734399175</v>
+        <v>17.53996905621455</v>
       </c>
       <c r="F4">
         <v>56.59618359979371</v>
       </c>
       <c r="G4">
-        <v>17.53996905621455</v>
+        <v>25.86384734399175</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>30.97102584181676</v>
+      </c>
+      <c r="C5">
         <v>33.32028191072827</v>
-      </c>
-      <c r="C5">
-        <v>30.97102584181676</v>
       </c>
       <c r="D5">
         <v>3.00117508813161</v>
       </c>
       <c r="E5">
-        <v>20.28122020972354</v>
+        <v>18.8512869399428</v>
       </c>
       <c r="F5">
         <v>60.86749285033365</v>
       </c>
       <c r="G5">
-        <v>18.8512869399428</v>
+        <v>20.28122020972354</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>27.11489475801045</v>
+      </c>
+      <c r="C6">
         <v>40.17964874648076</v>
-      </c>
-      <c r="C6">
-        <v>27.11489475801045</v>
       </c>
       <c r="D6">
         <v>2.488822155488822</v>
       </c>
       <c r="E6">
-        <v>24.01730977280923</v>
+        <v>16.20787754938494</v>
       </c>
       <c r="F6">
         <v>59.77481267780583</v>
       </c>
       <c r="G6">
-        <v>16.20787754938494</v>
+        <v>24.01730977280923</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>32.0493693204937</v>
+      </c>
+      <c r="C7">
         <v>38.5189203851892</v>
-      </c>
-      <c r="C7">
-        <v>32.0493693204937</v>
       </c>
       <c r="D7">
         <v>2.59612676056338</v>
       </c>
       <c r="E7">
-        <v>22.58269720101781</v>
+        <v>18.7897582697201</v>
       </c>
       <c r="F7">
         <v>58.62754452926209</v>
       </c>
       <c r="G7">
-        <v>18.7897582697201</v>
+        <v>22.58269720101781</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>27.7683519963805</v>
+      </c>
+      <c r="C8">
         <v>44.3954303811786</v>
-      </c>
-      <c r="C8">
-        <v>27.7683519963805</v>
       </c>
       <c r="D8">
         <v>2.252484076433121</v>
       </c>
       <c r="E8">
-        <v>25.78674200118258</v>
+        <v>16.12903225806452</v>
       </c>
       <c r="F8">
         <v>58.08422574075291</v>
       </c>
       <c r="G8">
-        <v>16.12903225806452</v>
+        <v>25.78674200118258</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>29.82231533209187</v>
+      </c>
+      <c r="C9">
         <v>31.04438237119802</v>
-      </c>
-      <c r="C9">
-        <v>29.82231533209187</v>
       </c>
       <c r="D9">
         <v>3.221194701324669</v>
       </c>
       <c r="E9">
-        <v>19.29820330399132</v>
+        <v>18.53852646810563</v>
       </c>
       <c r="F9">
         <v>62.16327022790304</v>
       </c>
       <c r="G9">
-        <v>18.53852646810563</v>
+        <v>19.29820330399132</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.87323943661972</v>
+      </c>
+      <c r="C10">
         <v>40.14781759866127</v>
-      </c>
-      <c r="C10">
-        <v>28.87323943661972</v>
       </c>
       <c r="D10">
         <v>2.490795415074678</v>
       </c>
       <c r="E10">
-        <v>23.75314549729796</v>
+        <v>17.08262860443051</v>
       </c>
       <c r="F10">
         <v>59.16422589827152</v>
       </c>
       <c r="G10">
-        <v>17.08262860443051</v>
+        <v>23.75314549729796</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>30.26751592356688</v>
+      </c>
+      <c r="C11">
         <v>44.71337579617835</v>
-      </c>
-      <c r="C11">
-        <v>30.26751592356688</v>
       </c>
       <c r="D11">
         <v>2.236467236467237</v>
       </c>
       <c r="E11">
-        <v>25.55329062317996</v>
+        <v>17.29761211415259</v>
       </c>
       <c r="F11">
         <v>57.14909726266744</v>
       </c>
       <c r="G11">
-        <v>17.29761211415259</v>
+        <v>25.55329062317996</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>29.07125307125307</v>
+      </c>
+      <c r="C12">
         <v>38.57002457002457</v>
-      </c>
-      <c r="C12">
-        <v>29.07125307125307</v>
       </c>
       <c r="D12">
         <v>2.592686966492547</v>
       </c>
       <c r="E12">
-        <v>23.00747471786604</v>
+        <v>17.34134544921589</v>
       </c>
       <c r="F12">
         <v>59.65117983291807</v>
       </c>
       <c r="G12">
-        <v>17.34134544921589</v>
+        <v>23.00747471786604</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>30.38408067561679</v>
+      </c>
+      <c r="C13">
         <v>27.84844271989708</v>
-      </c>
-      <c r="C13">
-        <v>30.38408067561679</v>
       </c>
       <c r="D13">
         <v>3.59086506221593</v>
       </c>
       <c r="E13">
-        <v>17.59969576563463</v>
+        <v>19.20217160391833</v>
       </c>
       <c r="F13">
         <v>63.19813263044703</v>
       </c>
       <c r="G13">
-        <v>19.20217160391833</v>
+        <v>17.59969576563463</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>31.28721942281264</v>
+      </c>
+      <c r="C14">
         <v>36.39486944571691</v>
-      </c>
-      <c r="C14">
-        <v>31.28721942281264</v>
       </c>
       <c r="D14">
         <v>2.747640025173065</v>
       </c>
       <c r="E14">
-        <v>21.7046851523016</v>
+        <v>18.65865318945499</v>
       </c>
       <c r="F14">
         <v>59.63666165824341</v>
       </c>
       <c r="G14">
-        <v>18.65865318945499</v>
+        <v>21.7046851523016</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>27.88764328001008</v>
+      </c>
+      <c r="C15">
         <v>38.56279128353697</v>
-      </c>
-      <c r="C15">
-        <v>27.88764328001008</v>
       </c>
       <c r="D15">
         <v>2.59317328107137</v>
       </c>
       <c r="E15">
-        <v>23.16773241515002</v>
+        <v>16.75432290287185</v>
       </c>
       <c r="F15">
         <v>60.07794468197813</v>
       </c>
       <c r="G15">
-        <v>16.75432290287185</v>
+        <v>23.16773241515002</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>28.14875135722041</v>
+      </c>
+      <c r="C16">
         <v>26.26673905175534</v>
-      </c>
-      <c r="C16">
-        <v>28.14875135722041</v>
       </c>
       <c r="D16">
         <v>3.807096107475026</v>
       </c>
       <c r="E16">
-        <v>17.01043009492558</v>
+        <v>18.22922770420719</v>
       </c>
       <c r="F16">
         <v>64.76034220086721</v>
       </c>
       <c r="G16">
-        <v>18.22922770420719</v>
+        <v>17.01043009492558</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>31.46112067823553</v>
+      </c>
+      <c r="C17">
         <v>43.59517816929394</v>
-      </c>
-      <c r="C17">
-        <v>31.46112067823553</v>
       </c>
       <c r="D17">
         <v>2.293831662108782</v>
       </c>
       <c r="E17">
-        <v>24.90351872871737</v>
+        <v>17.97200151343171</v>
       </c>
       <c r="F17">
         <v>57.12447975785093</v>
       </c>
       <c r="G17">
-        <v>17.97200151343171</v>
+        <v>24.90351872871737</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>29.63004737198285</v>
+      </c>
+      <c r="C18">
         <v>44.74396571170765</v>
-      </c>
-      <c r="C18">
-        <v>29.63004737198285</v>
       </c>
       <c r="D18">
         <v>2.234938240483993</v>
       </c>
       <c r="E18">
-        <v>25.65976714100905</v>
+        <v>16.99223803363519</v>
       </c>
       <c r="F18">
         <v>57.34799482535576</v>
       </c>
       <c r="G18">
-        <v>16.99223803363519</v>
+        <v>25.65976714100905</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>28.54755139562092</v>
+      </c>
+      <c r="C19">
         <v>42.5037606551897</v>
-      </c>
-      <c r="C19">
-        <v>28.54755139562092</v>
       </c>
       <c r="D19">
         <v>2.35273299252851</v>
       </c>
       <c r="E19">
-        <v>24.8485440687903</v>
+        <v>16.68946648426813</v>
       </c>
       <c r="F19">
         <v>58.46198944694157</v>
       </c>
       <c r="G19">
-        <v>16.68946648426813</v>
+        <v>24.8485440687903</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>30.49937645719243</v>
+      </c>
+      <c r="C20">
         <v>30.84096947351298</v>
-      </c>
-      <c r="C20">
-        <v>30.49937645719243</v>
       </c>
       <c r="D20">
         <v>3.242440225035162</v>
       </c>
       <c r="E20">
-        <v>19.11547250974593</v>
+        <v>18.90375050410001</v>
       </c>
       <c r="F20">
         <v>61.98077698615405</v>
       </c>
       <c r="G20">
-        <v>18.90375050410001</v>
+        <v>19.11547250974593</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>30.24373988384271</v>
+      </c>
+      <c r="C21">
         <v>31.66952299343045</v>
-      </c>
-      <c r="C21">
-        <v>30.24373988384271</v>
       </c>
       <c r="D21">
         <v>3.1576099210823</v>
       </c>
       <c r="E21">
-        <v>19.5595607368096</v>
+        <v>18.67897622862855</v>
       </c>
       <c r="F21">
-        <v>61.76146303456183</v>
+        <v>61.76146303456184</v>
       </c>
       <c r="G21">
-        <v>18.67897622862855</v>
+        <v>19.55956073680961</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>33.14939991722996</v>
+      </c>
+      <c r="C22">
         <v>34.58408056283626</v>
-      </c>
-      <c r="C22">
-        <v>33.14939991722996</v>
       </c>
       <c r="D22">
         <v>2.891503789389709</v>
       </c>
       <c r="E22">
-        <v>20.61847191380871</v>
+        <v>19.76313841598815</v>
       </c>
       <c r="F22">
-        <v>59.61838967020315</v>
+        <v>59.61838967020314</v>
       </c>
       <c r="G22">
-        <v>19.76313841598816</v>
+        <v>20.6184719138087</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>28.34989026221555</v>
+      </c>
+      <c r="C23">
         <v>34.77243848908398</v>
-      </c>
-      <c r="C23">
-        <v>28.34989026221555</v>
       </c>
       <c r="D23">
         <v>2.875840877003571</v>
       </c>
       <c r="E23">
-        <v>21.31678646036186</v>
+        <v>17.37952767057324</v>
       </c>
       <c r="F23">
         <v>61.3036858690649</v>
       </c>
       <c r="G23">
-        <v>17.37952767057324</v>
+        <v>21.31678646036186</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>30.11883282523486</v>
+      </c>
+      <c r="C24">
         <v>33.46606109624837</v>
-      </c>
-      <c r="C24">
-        <v>30.11883282523486</v>
       </c>
       <c r="D24">
         <v>2.98810187767243</v>
       </c>
       <c r="E24">
+        <v>18.41174457079831</v>
+      </c>
+      <c r="F24">
+        <v>61.13033887346442</v>
+      </c>
+      <c r="G24">
         <v>20.45791655573727</v>
-      </c>
-      <c r="F24">
-        <v>61.13033887346441</v>
-      </c>
-      <c r="G24">
-        <v>18.41174457079831</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>28.07545106615637</v>
+      </c>
+      <c r="C25">
         <v>44.37761982868598</v>
-      </c>
-      <c r="C25">
-        <v>28.07545106615637</v>
       </c>
       <c r="D25">
         <v>2.253388090349076</v>
       </c>
       <c r="E25">
-        <v>25.7331571994716</v>
+        <v>16.28005284015852</v>
       </c>
       <c r="F25">
         <v>57.98678996036988</v>
       </c>
       <c r="G25">
-        <v>16.28005284015852</v>
+        <v>25.7331571994716</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>35.37363875328577</v>
+      </c>
+      <c r="C26">
         <v>32.83890349230191</v>
-      </c>
-      <c r="C26">
-        <v>35.37363875328577</v>
       </c>
       <c r="D26">
         <v>3.045168667810177</v>
       </c>
       <c r="E26">
-        <v>19.52226811028016</v>
+        <v>21.02913271570488</v>
       </c>
       <c r="F26">
         <v>59.44859917401496</v>
       </c>
       <c r="G26">
-        <v>21.02913271570488</v>
+        <v>19.52226811028016</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>32.14969795196699</v>
+      </c>
+      <c r="C27">
         <v>33.87358184764992</v>
-      </c>
-      <c r="C27">
-        <v>32.14969795196699</v>
       </c>
       <c r="D27">
         <v>2.952153110047847</v>
       </c>
       <c r="E27">
-        <v>20.40291089811856</v>
+        <v>19.3645722399716</v>
       </c>
       <c r="F27">
         <v>60.23251686190984</v>
       </c>
       <c r="G27">
-        <v>19.3645722399716</v>
+        <v>20.40291089811856</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>27.66103243490178</v>
+      </c>
+      <c r="C28">
         <v>39.85838282320695</v>
-      </c>
-      <c r="C28">
-        <v>27.66103243490178</v>
       </c>
       <c r="D28">
         <v>2.508882521489971</v>
       </c>
       <c r="E28">
-        <v>23.79329151895282</v>
+        <v>16.51213526043087</v>
       </c>
       <c r="F28">
         <v>59.69457322061631</v>
       </c>
       <c r="G28">
-        <v>16.51213526043087</v>
+        <v>23.79329151895282</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>28.63858253480383</v>
+      </c>
+      <c r="C29">
         <v>38.38365575845236</v>
-      </c>
-      <c r="C29">
-        <v>28.63858253480383</v>
       </c>
       <c r="D29">
         <v>2.605275553462082</v>
       </c>
       <c r="E29">
-        <v>22.98116475427582</v>
+        <v>17.14656852132496</v>
       </c>
       <c r="F29">
         <v>59.87226672439922</v>
       </c>
       <c r="G29">
-        <v>17.14656852132496</v>
+        <v>22.98116475427582</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>30.7075030092283</v>
+      </c>
+      <c r="C30">
         <v>39.49444964557978</v>
-      </c>
-      <c r="C30">
-        <v>30.7075030092283</v>
       </c>
       <c r="D30">
         <v>2.53200135455469</v>
       </c>
       <c r="E30">
-        <v>23.2044633034732</v>
+        <v>18.04180418041804</v>
       </c>
       <c r="F30">
         <v>58.75373251610876</v>
       </c>
       <c r="G30">
-        <v>18.04180418041804</v>
+        <v>23.2044633034732</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>30.13719512195122</v>
+      </c>
+      <c r="C31">
         <v>33.64329268292683</v>
-      </c>
-      <c r="C31">
-        <v>30.13719512195122</v>
       </c>
       <c r="D31">
         <v>2.972360670593566</v>
       </c>
       <c r="E31">
-        <v>20.54169769173492</v>
+        <v>18.40096798212956</v>
       </c>
       <c r="F31">
         <v>61.05733432613552</v>
       </c>
       <c r="G31">
-        <v>18.40096798212956</v>
+        <v>20.54169769173492</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>29.99212115906504</v>
+      </c>
+      <c r="C32">
         <v>43.20231112667425</v>
-      </c>
-      <c r="C32">
-        <v>29.99212115906504</v>
       </c>
       <c r="D32">
         <v>2.314690982776089</v>
       </c>
       <c r="E32">
-        <v>24.9443995147594</v>
+        <v>17.31702385766275</v>
       </c>
       <c r="F32">
         <v>57.73857662757784</v>
       </c>
       <c r="G32">
-        <v>17.31702385766275</v>
+        <v>24.9443995147594</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>27.47954405713475</v>
+      </c>
+      <c r="C33">
         <v>38.69365747528733</v>
-      </c>
-      <c r="C33">
-        <v>27.47954405713475</v>
       </c>
       <c r="D33">
         <v>2.584402884732918</v>
       </c>
       <c r="E33">
-        <v>23.28513690442307</v>
+        <v>16.53668810838504</v>
       </c>
       <c r="F33">
         <v>60.17817498719189</v>
       </c>
       <c r="G33">
-        <v>16.53668810838504</v>
+        <v>23.28513690442307</v>
       </c>
     </row>
   </sheetData>
